--- a/examples/sample_life_care_plan.xlsx
+++ b/examples/sample_life_care_plan.xlsx
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -216,10 +216,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -832,10 +837,10 @@
         <v>2809609.01</v>
       </c>
     </row>
-    <row r="26" ht="90" customHeight="1">
+    <row r="26" ht="81" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>This workbook was generated by PA-LCP-Tool v0.1.0 on 2026-06-23 22:48. It presents cost projections based on the inputs and published rate/source citations documented on the Assumptions &amp; Rates and Data Sources tabs. Costs are stated in current (base-year) dollars, grown to the year incurred using the cited medical price series, and discounted to present value at the cited rate using the stated timing convention. Medical care opinions and their foundation are addressed on the Medical Foundation tab and remain the responsibility of the qualified clinician(s) of record.</t>
+          <t>This workbook was generated by PA-LCP-Tool v0.1.0 on 2026-06-23 23:16. It presents cost projections based on the inputs and published rate/source citations documented on the Assumptions &amp; Rates and Data Sources tabs. Costs are stated in current (base-year) dollars, grown to the year incurred using the cited medical price series, and discounted to present value at the cited rate using the stated timing convention. Medical care opinions and their foundation are addressed on the Medical Foundation tab and remain the responsibility of the qualified clinician(s) of record.</t>
         </is>
       </c>
     </row>
@@ -902,7 +907,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>No findings. All checks passed.</t>
@@ -1183,7 +1188,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="29" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Detailed rate sources and formulas appear on the Assumptions &amp; Rates tab. Per-item detail appears on the Current-Cost Tables and PV Projection tabs.</t>
@@ -1395,12 +1400,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="J8" s="22" t="inlineStr">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t>Physician Services subtotal</t>
         </is>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="24" t="n">
         <v>54112</v>
       </c>
     </row>
@@ -1504,12 +1518,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="J12" s="22" t="inlineStr">
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t>Therapies subtotal</t>
         </is>
       </c>
-      <c r="K12" s="23" t="n">
+      <c r="K12" s="24" t="n">
         <v>312300</v>
       </c>
     </row>
@@ -1570,12 +1593,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="J15" s="22" t="inlineStr">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t>Diagnostics subtotal</t>
         </is>
       </c>
-      <c r="K15" s="23" t="n">
+      <c r="K15" s="24" t="n">
         <v>22515</v>
       </c>
     </row>
@@ -1667,12 +1699,21 @@
       </c>
     </row>
     <row r="19">
-      <c r="J19" s="22" t="inlineStr">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="23" t="inlineStr">
         <is>
           <t>Medications subtotal</t>
         </is>
       </c>
-      <c r="K19" s="23" t="n">
+      <c r="K19" s="24" t="n">
         <v>65360</v>
       </c>
     </row>
@@ -1772,12 +1813,21 @@
       </c>
     </row>
     <row r="23">
-      <c r="J23" s="22" t="inlineStr">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="23" t="inlineStr">
         <is>
           <t>Durable Medical Equipment subtotal</t>
         </is>
       </c>
-      <c r="K23" s="23" t="n">
+      <c r="K23" s="24" t="n">
         <v>33520</v>
       </c>
     </row>
@@ -1879,12 +1929,21 @@
       </c>
     </row>
     <row r="27">
-      <c r="J27" s="22" t="inlineStr">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="23" t="inlineStr">
         <is>
           <t>Surgeries/Procedures subtotal</t>
         </is>
       </c>
-      <c r="K27" s="23" t="n">
+      <c r="K27" s="24" t="n">
         <v>207000</v>
       </c>
     </row>
@@ -1941,12 +2000,21 @@
       </c>
     </row>
     <row r="30">
-      <c r="J30" s="22" t="inlineStr">
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="23" t="inlineStr">
         <is>
           <t>Attendant Care subtotal</t>
         </is>
       </c>
-      <c r="K30" s="23" t="n">
+      <c r="K30" s="24" t="n">
         <v>2496600</v>
       </c>
     </row>
@@ -2001,12 +2069,21 @@
       </c>
     </row>
     <row r="33">
-      <c r="J33" s="22" t="inlineStr">
+      <c r="A33" s="22" t="n"/>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="23" t="inlineStr">
         <is>
           <t>Home Modifications subtotal</t>
         </is>
       </c>
-      <c r="K33" s="23" t="n">
+      <c r="K33" s="24" t="n">
         <v>28500</v>
       </c>
     </row>
@@ -2063,22 +2140,40 @@
       </c>
     </row>
     <row r="36">
-      <c r="J36" s="22" t="inlineStr">
+      <c r="A36" s="22" t="n"/>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="22" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="23" t="inlineStr">
         <is>
           <t>Transportation subtotal</t>
         </is>
       </c>
-      <c r="K36" s="23" t="n">
+      <c r="K36" s="24" t="n">
         <v>132000</v>
       </c>
     </row>
     <row r="37">
-      <c r="J37" s="22" t="inlineStr">
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="25" t="n"/>
+      <c r="D37" s="25" t="n"/>
+      <c r="E37" s="25" t="n"/>
+      <c r="F37" s="25" t="n"/>
+      <c r="G37" s="25" t="n"/>
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="25" t="n"/>
+      <c r="J37" s="26" t="inlineStr">
         <is>
           <t>LIFETIME TOTAL (undiscounted)</t>
         </is>
       </c>
-      <c r="K37" s="24" t="n">
+      <c r="K37" s="27" t="n">
         <v>3351907</v>
       </c>
     </row>
@@ -2205,13 +2300,13 @@
           <t>Medical Care Services</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="28" t="n">
         <v>0.032</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="28" t="n">
         <v>0.01065891472868197</v>
       </c>
       <c r="G6" s="6" t="n">
@@ -2240,13 +2335,13 @@
           <t>Medical Care Services</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="28" t="n">
         <v>0.032</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="28" t="n">
         <v>0.01065891472868197</v>
       </c>
       <c r="G7" s="6" t="n">
@@ -2260,18 +2355,23 @@
       </c>
     </row>
     <row r="8">
-      <c r="F8" s="22" t="inlineStr">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Physician Services subtotal</t>
         </is>
       </c>
-      <c r="G8" s="23" t="n">
+      <c r="G8" s="24" t="n">
         <v>54112</v>
       </c>
-      <c r="H8" s="23" t="n">
+      <c r="H8" s="24" t="n">
         <v>104426.94</v>
       </c>
-      <c r="I8" s="23" t="n">
+      <c r="I8" s="24" t="n">
         <v>44538.68</v>
       </c>
     </row>
@@ -2306,13 +2406,13 @@
           <t>Medical Care Services</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="28" t="n">
         <v>0.032</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="28" t="n">
         <v>0.01065891472868197</v>
       </c>
       <c r="G10" s="6" t="n">
@@ -2341,13 +2441,13 @@
           <t>Medical Care Services</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="28" t="n">
         <v>0.032</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="28" t="n">
         <v>0.01065891472868197</v>
       </c>
       <c r="G11" s="6" t="n">
@@ -2361,18 +2461,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="F12" s="22" t="inlineStr">
+      <c r="A12" s="22" t="n"/>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>Therapies subtotal</t>
         </is>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="24" t="n">
         <v>312300</v>
       </c>
-      <c r="H12" s="23" t="n">
+      <c r="H12" s="24" t="n">
         <v>552099.14</v>
       </c>
-      <c r="I12" s="23" t="n">
+      <c r="I12" s="24" t="n">
         <v>264605.71</v>
       </c>
     </row>
@@ -2407,13 +2512,13 @@
           <t>Hospital &amp; Facility Services</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="28" t="n">
         <v>0.038</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="28" t="n">
         <v>0.00481695568400764</v>
       </c>
       <c r="G14" s="6" t="n">
@@ -2427,18 +2532,23 @@
       </c>
     </row>
     <row r="15">
-      <c r="F15" s="22" t="inlineStr">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>Diagnostics subtotal</t>
         </is>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="G15" s="24" t="n">
         <v>22515</v>
       </c>
-      <c r="H15" s="23" t="n">
+      <c r="H15" s="24" t="n">
         <v>48728.04</v>
       </c>
-      <c r="I15" s="23" t="n">
+      <c r="I15" s="24" t="n">
         <v>20628.37</v>
       </c>
     </row>
@@ -2473,13 +2583,13 @@
           <t>Prescription Drugs</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="28" t="n">
         <v>0.025</v>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F17" s="25" t="n">
+      <c r="F17" s="28" t="n">
         <v>0.01756097560975611</v>
       </c>
       <c r="G17" s="6" t="n">
@@ -2508,13 +2618,13 @@
           <t>Prescription Drugs</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="28" t="n">
         <v>0.025</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="28" t="n">
         <v>0.01756097560975611</v>
       </c>
       <c r="G18" s="6" t="n">
@@ -2528,18 +2638,23 @@
       </c>
     </row>
     <row r="19">
-      <c r="F19" s="22" t="inlineStr">
+      <c r="A19" s="22" t="n"/>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>Medications subtotal</t>
         </is>
       </c>
-      <c r="G19" s="23" t="n">
+      <c r="G19" s="24" t="n">
         <v>65360</v>
       </c>
-      <c r="H19" s="23" t="n">
+      <c r="H19" s="24" t="n">
         <v>108360.58</v>
       </c>
-      <c r="I19" s="23" t="n">
+      <c r="I19" s="24" t="n">
         <v>47813.26</v>
       </c>
     </row>
@@ -2574,13 +2689,13 @@
           <t>Durable Medical Equipment / Supplies</t>
         </is>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="F21" s="28" t="n">
         <v>0.02254901960784306</v>
       </c>
       <c r="G21" s="6" t="n">
@@ -2609,13 +2724,13 @@
           <t>Durable Medical Equipment / Supplies</t>
         </is>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D22" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F22" s="25" t="n">
+      <c r="F22" s="28" t="n">
         <v>0.02254901960784306</v>
       </c>
       <c r="G22" s="6" t="n">
@@ -2629,18 +2744,23 @@
       </c>
     </row>
     <row r="23">
-      <c r="F23" s="22" t="inlineStr">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>Durable Medical Equipment subtotal</t>
         </is>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G23" s="24" t="n">
         <v>33520</v>
       </c>
-      <c r="H23" s="23" t="n">
+      <c r="H23" s="24" t="n">
         <v>49473.55</v>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I23" s="24" t="n">
         <v>22944.01</v>
       </c>
     </row>
@@ -2675,13 +2795,13 @@
           <t>Hospital &amp; Facility Services</t>
         </is>
       </c>
-      <c r="D25" s="25" t="n">
+      <c r="D25" s="28" t="n">
         <v>0.038</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F25" s="25" t="n">
+      <c r="F25" s="28" t="n">
         <v>0.00481695568400764</v>
       </c>
       <c r="G25" s="6" t="n">
@@ -2710,13 +2830,13 @@
           <t>Hospital &amp; Facility Services</t>
         </is>
       </c>
-      <c r="D26" s="25" t="n">
+      <c r="D26" s="28" t="n">
         <v>0.038</v>
       </c>
-      <c r="E26" s="25" t="n">
+      <c r="E26" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F26" s="25" t="n">
+      <c r="F26" s="28" t="n">
         <v>0.00481695568400764</v>
       </c>
       <c r="G26" s="6" t="n">
@@ -2730,18 +2850,23 @@
       </c>
     </row>
     <row r="27">
-      <c r="F27" s="22" t="inlineStr">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>Surgeries/Procedures subtotal</t>
         </is>
       </c>
-      <c r="G27" s="23" t="n">
+      <c r="G27" s="24" t="n">
         <v>207000</v>
       </c>
-      <c r="H27" s="23" t="n">
+      <c r="H27" s="24" t="n">
         <v>389740.26</v>
       </c>
-      <c r="I27" s="23" t="n">
+      <c r="I27" s="24" t="n">
         <v>193108.53</v>
       </c>
     </row>
@@ -2776,13 +2901,13 @@
           <t>Attendant / Home-Health Care (wage-based)</t>
         </is>
       </c>
-      <c r="D29" s="25" t="n">
+      <c r="D29" s="28" t="n">
         <v>0.033</v>
       </c>
-      <c r="E29" s="25" t="n">
+      <c r="E29" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F29" s="25" t="n">
+      <c r="F29" s="28" t="n">
         <v>0.009680542110358292</v>
       </c>
       <c r="G29" s="6" t="n">
@@ -2796,18 +2921,23 @@
       </c>
     </row>
     <row r="30">
-      <c r="F30" s="22" t="inlineStr">
+      <c r="A30" s="22" t="n"/>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>Attendant Care subtotal</t>
         </is>
       </c>
-      <c r="G30" s="23" t="n">
+      <c r="G30" s="24" t="n">
         <v>2496600</v>
       </c>
-      <c r="H30" s="23" t="n">
+      <c r="H30" s="24" t="n">
         <v>4925371.48</v>
       </c>
-      <c r="I30" s="23" t="n">
+      <c r="I30" s="24" t="n">
         <v>2090614.98</v>
       </c>
     </row>
@@ -2842,13 +2972,13 @@
           <t>General (CPI-U, all items)</t>
         </is>
       </c>
-      <c r="D32" s="25" t="n">
+      <c r="D32" s="28" t="n">
         <v>0.024</v>
       </c>
-      <c r="E32" s="25" t="n">
+      <c r="E32" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F32" s="25" t="n">
+      <c r="F32" s="28" t="n">
         <v>0.0185546875</v>
       </c>
       <c r="G32" s="6" t="n">
@@ -2862,18 +2992,23 @@
       </c>
     </row>
     <row r="33">
-      <c r="F33" s="22" t="inlineStr">
+      <c r="A33" s="22" t="n"/>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>Home Modifications subtotal</t>
         </is>
       </c>
-      <c r="G33" s="23" t="n">
+      <c r="G33" s="24" t="n">
         <v>28500</v>
       </c>
-      <c r="H33" s="23" t="n">
+      <c r="H33" s="24" t="n">
         <v>28839.97</v>
       </c>
-      <c r="I33" s="23" t="n">
+      <c r="I33" s="24" t="n">
         <v>28239.22</v>
       </c>
     </row>
@@ -2908,13 +3043,13 @@
           <t>General (CPI-U, all items)</t>
         </is>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D35" s="28" t="n">
         <v>0.024</v>
       </c>
-      <c r="E35" s="25" t="n">
+      <c r="E35" s="28" t="n">
         <v>0.043</v>
       </c>
-      <c r="F35" s="25" t="n">
+      <c r="F35" s="28" t="n">
         <v>0.0185546875</v>
       </c>
       <c r="G35" s="6" t="n">
@@ -2928,34 +3063,44 @@
       </c>
     </row>
     <row r="36">
-      <c r="F36" s="22" t="inlineStr">
+      <c r="A36" s="22" t="n"/>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>Transportation subtotal</t>
         </is>
       </c>
-      <c r="G36" s="23" t="n">
+      <c r="G36" s="24" t="n">
         <v>132000</v>
       </c>
-      <c r="H36" s="23" t="n">
+      <c r="H36" s="24" t="n">
         <v>210514.92</v>
       </c>
-      <c r="I36" s="23" t="n">
+      <c r="I36" s="24" t="n">
         <v>97116.24000000001</v>
       </c>
     </row>
     <row r="37">
-      <c r="F37" s="22" t="inlineStr">
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="25" t="n"/>
+      <c r="D37" s="25" t="n"/>
+      <c r="E37" s="25" t="n"/>
+      <c r="F37" s="26" t="inlineStr">
         <is>
           <t>LIFETIME TOTAL</t>
         </is>
       </c>
-      <c r="G37" s="24" t="n">
+      <c r="G37" s="27" t="n">
         <v>3351907</v>
       </c>
-      <c r="H37" s="24" t="n">
+      <c r="H37" s="27" t="n">
         <v>6417554.89</v>
       </c>
-      <c r="I37" s="24" t="n">
+      <c r="I37" s="27" t="n">
         <v>2809609.01</v>
       </c>
     </row>
@@ -3133,7 +3278,7 @@
       <c r="M5" s="6" t="n">
         <v>136061.84</v>
       </c>
-      <c r="N5" s="26" t="n">
+      <c r="N5" s="29" t="n">
         <v>0.9792</v>
       </c>
       <c r="O5" s="6" t="n">
@@ -3144,13 +3289,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="30" t="n">
         <v>2027</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="30" t="n">
         <v>43</v>
       </c>
       <c r="D6" s="13" t="n">
@@ -3183,7 +3328,7 @@
       <c r="M6" s="13" t="n">
         <v>83897.59</v>
       </c>
-      <c r="N6" s="28" t="n">
+      <c r="N6" s="31" t="n">
         <v>0.9388</v>
       </c>
       <c r="O6" s="13" t="n">
@@ -3233,7 +3378,7 @@
       <c r="M7" s="6" t="n">
         <v>87935.14999999999</v>
       </c>
-      <c r="N7" s="26" t="n">
+      <c r="N7" s="29" t="n">
         <v>0.9001</v>
       </c>
       <c r="O7" s="6" t="n">
@@ -3244,13 +3389,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="30" t="n">
         <v>2029</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="30" t="n">
         <v>45</v>
       </c>
       <c r="D8" s="13" t="n">
@@ -3283,7 +3428,7 @@
       <c r="M8" s="13" t="n">
         <v>148711.34</v>
       </c>
-      <c r="N8" s="28" t="n">
+      <c r="N8" s="31" t="n">
         <v>0.863</v>
       </c>
       <c r="O8" s="13" t="n">
@@ -3333,7 +3478,7 @@
       <c r="M9" s="6" t="n">
         <v>130445.53</v>
       </c>
-      <c r="N9" s="26" t="n">
+      <c r="N9" s="29" t="n">
         <v>0.8274</v>
       </c>
       <c r="O9" s="6" t="n">
@@ -3344,13 +3489,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="30" t="n">
         <v>2031</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="30" t="n">
         <v>47</v>
       </c>
       <c r="D10" s="13" t="n">
@@ -3383,7 +3528,7 @@
       <c r="M10" s="13" t="n">
         <v>98158.5</v>
       </c>
-      <c r="N10" s="28" t="n">
+      <c r="N10" s="31" t="n">
         <v>0.7933</v>
       </c>
       <c r="O10" s="13" t="n">
@@ -3433,7 +3578,7 @@
       <c r="M11" s="6" t="n">
         <v>100015.74</v>
       </c>
-      <c r="N11" s="26" t="n">
+      <c r="N11" s="29" t="n">
         <v>0.7606000000000001</v>
       </c>
       <c r="O11" s="6" t="n">
@@ -3444,13 +3589,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="30" t="n">
         <v>2033</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="30" t="n">
         <v>49</v>
       </c>
       <c r="D12" s="13" t="n">
@@ -3483,7 +3628,7 @@
       <c r="M12" s="13" t="n">
         <v>128002.76</v>
       </c>
-      <c r="N12" s="28" t="n">
+      <c r="N12" s="31" t="n">
         <v>0.7292</v>
       </c>
       <c r="O12" s="13" t="n">
@@ -3533,7 +3678,7 @@
       <c r="M13" s="6" t="n">
         <v>106666.3</v>
       </c>
-      <c r="N13" s="26" t="n">
+      <c r="N13" s="29" t="n">
         <v>0.6992</v>
       </c>
       <c r="O13" s="6" t="n">
@@ -3544,13 +3689,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="30" t="n">
         <v>2035</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="30" t="n">
         <v>51</v>
       </c>
       <c r="D14" s="13" t="n">
@@ -3583,7 +3728,7 @@
       <c r="M14" s="13" t="n">
         <v>108467.14</v>
       </c>
-      <c r="N14" s="28" t="n">
+      <c r="N14" s="31" t="n">
         <v>0.6703</v>
       </c>
       <c r="O14" s="13" t="n">
@@ -3633,7 +3778,7 @@
       <c r="M15" s="6" t="n">
         <v>116813.31</v>
       </c>
-      <c r="N15" s="26" t="n">
+      <c r="N15" s="29" t="n">
         <v>0.6427</v>
       </c>
       <c r="O15" s="6" t="n">
@@ -3644,13 +3789,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="30" t="n">
         <v>2037</v>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="30" t="n">
         <v>53</v>
       </c>
       <c r="D16" s="13" t="n">
@@ -3683,7 +3828,7 @@
       <c r="M16" s="13" t="n">
         <v>163265.45</v>
       </c>
-      <c r="N16" s="28" t="n">
+      <c r="N16" s="31" t="n">
         <v>0.6162</v>
       </c>
       <c r="O16" s="13" t="n">
@@ -3733,7 +3878,7 @@
       <c r="M17" s="6" t="n">
         <v>121326.81</v>
       </c>
-      <c r="N17" s="26" t="n">
+      <c r="N17" s="29" t="n">
         <v>0.5908</v>
       </c>
       <c r="O17" s="6" t="n">
@@ -3744,13 +3889,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n">
+      <c r="A18" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="30" t="n">
         <v>2039</v>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="30" t="n">
         <v>55</v>
       </c>
       <c r="D18" s="13" t="n">
@@ -3783,7 +3928,7 @@
       <c r="M18" s="13" t="n">
         <v>123336.69</v>
       </c>
-      <c r="N18" s="28" t="n">
+      <c r="N18" s="31" t="n">
         <v>0.5665</v>
       </c>
       <c r="O18" s="13" t="n">
@@ -3833,7 +3978,7 @@
       <c r="M19" s="6" t="n">
         <v>160427.24</v>
       </c>
-      <c r="N19" s="26" t="n">
+      <c r="N19" s="29" t="n">
         <v>0.5431</v>
       </c>
       <c r="O19" s="6" t="n">
@@ -3844,13 +3989,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="30" t="n">
         <v>2041</v>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="30" t="n">
         <v>57</v>
       </c>
       <c r="D20" s="13" t="n">
@@ -3883,7 +4028,7 @@
       <c r="M20" s="13" t="n">
         <v>134891.66</v>
       </c>
-      <c r="N20" s="28" t="n">
+      <c r="N20" s="31" t="n">
         <v>0.5207000000000001</v>
       </c>
       <c r="O20" s="13" t="n">
@@ -3933,7 +4078,7 @@
       <c r="M21" s="6" t="n">
         <v>138007.17</v>
       </c>
-      <c r="N21" s="26" t="n">
+      <c r="N21" s="29" t="n">
         <v>0.4992</v>
       </c>
       <c r="O21" s="6" t="n">
@@ -3944,13 +4089,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="27" t="n">
+      <c r="B22" s="30" t="n">
         <v>2043</v>
       </c>
-      <c r="C22" s="27" t="n">
+      <c r="C22" s="30" t="n">
         <v>59</v>
       </c>
       <c r="D22" s="13" t="n">
@@ -3983,7 +4128,7 @@
       <c r="M22" s="13" t="n">
         <v>140248.74</v>
       </c>
-      <c r="N22" s="28" t="n">
+      <c r="N22" s="31" t="n">
         <v>0.4787</v>
       </c>
       <c r="O22" s="13" t="n">
@@ -4033,7 +4178,7 @@
       <c r="M23" s="6" t="n">
         <v>200379.65</v>
       </c>
-      <c r="N23" s="26" t="n">
+      <c r="N23" s="29" t="n">
         <v>0.4589</v>
       </c>
       <c r="O23" s="6" t="n">
@@ -4044,13 +4189,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="n">
+      <c r="A24" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="27" t="n">
+      <c r="B24" s="30" t="n">
         <v>2045</v>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C24" s="30" t="n">
         <v>61</v>
       </c>
       <c r="D24" s="13" t="n">
@@ -4083,7 +4228,7 @@
       <c r="M24" s="13" t="n">
         <v>140667.1</v>
       </c>
-      <c r="N24" s="28" t="n">
+      <c r="N24" s="31" t="n">
         <v>0.44</v>
       </c>
       <c r="O24" s="13" t="n">
@@ -4133,7 +4278,7 @@
       <c r="M25" s="6" t="n">
         <v>151533.61</v>
       </c>
-      <c r="N25" s="26" t="n">
+      <c r="N25" s="29" t="n">
         <v>0.4219</v>
       </c>
       <c r="O25" s="6" t="n">
@@ -4144,13 +4289,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n">
+      <c r="A26" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="27" t="n">
+      <c r="B26" s="30" t="n">
         <v>2047</v>
       </c>
-      <c r="C26" s="27" t="n">
+      <c r="C26" s="30" t="n">
         <v>63</v>
       </c>
       <c r="D26" s="13" t="n">
@@ -4183,7 +4328,7 @@
       <c r="M26" s="13" t="n">
         <v>186649.18</v>
       </c>
-      <c r="N26" s="28" t="n">
+      <c r="N26" s="31" t="n">
         <v>0.4045</v>
       </c>
       <c r="O26" s="13" t="n">
@@ -4233,7 +4378,7 @@
       <c r="M27" s="6" t="n">
         <v>157664.29</v>
       </c>
-      <c r="N27" s="26" t="n">
+      <c r="N27" s="29" t="n">
         <v>0.3878</v>
       </c>
       <c r="O27" s="6" t="n">
@@ -4244,13 +4389,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
+      <c r="A28" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="27" t="n">
+      <c r="B28" s="30" t="n">
         <v>2049</v>
       </c>
-      <c r="C28" s="27" t="n">
+      <c r="C28" s="30" t="n">
         <v>65</v>
       </c>
       <c r="D28" s="13" t="n">
@@ -4283,7 +4428,7 @@
       <c r="M28" s="13" t="n">
         <v>159987.88</v>
       </c>
-      <c r="N28" s="28" t="n">
+      <c r="N28" s="31" t="n">
         <v>0.3718</v>
       </c>
       <c r="O28" s="13" t="n">
@@ -4333,7 +4478,7 @@
       <c r="M29" s="6" t="n">
         <v>168174.98</v>
       </c>
-      <c r="N29" s="26" t="n">
+      <c r="N29" s="29" t="n">
         <v>0.3565</v>
       </c>
       <c r="O29" s="6" t="n">
@@ -4344,13 +4489,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n">
+      <c r="A30" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="27" t="n">
+      <c r="B30" s="30" t="n">
         <v>2051</v>
       </c>
-      <c r="C30" s="27" t="n">
+      <c r="C30" s="30" t="n">
         <v>67</v>
       </c>
       <c r="D30" s="13" t="n">
@@ -4383,7 +4528,7 @@
       <c r="M30" s="13" t="n">
         <v>254973.33</v>
       </c>
-      <c r="N30" s="28" t="n">
+      <c r="N30" s="31" t="n">
         <v>0.3418</v>
       </c>
       <c r="O30" s="13" t="n">
@@ -4433,7 +4578,7 @@
       <c r="M31" s="6" t="n">
         <v>179387.91</v>
       </c>
-      <c r="N31" s="26" t="n">
+      <c r="N31" s="29" t="n">
         <v>0.3277</v>
       </c>
       <c r="O31" s="6" t="n">
@@ -4444,13 +4589,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="n">
+      <c r="A32" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="27" t="n">
+      <c r="B32" s="30" t="n">
         <v>2053</v>
       </c>
-      <c r="C32" s="27" t="n">
+      <c r="C32" s="30" t="n">
         <v>69</v>
       </c>
       <c r="D32" s="13" t="n">
@@ -4483,7 +4628,7 @@
       <c r="M32" s="13" t="n">
         <v>181967.48</v>
       </c>
-      <c r="N32" s="28" t="n">
+      <c r="N32" s="31" t="n">
         <v>0.3142</v>
       </c>
       <c r="O32" s="13" t="n">
@@ -4533,7 +4678,7 @@
       <c r="M33" s="6" t="n">
         <v>234598.62</v>
       </c>
-      <c r="N33" s="26" t="n">
+      <c r="N33" s="29" t="n">
         <v>0.3012</v>
       </c>
       <c r="O33" s="6" t="n">
@@ -4544,13 +4689,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="n">
+      <c r="A34" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="27" t="n">
+      <c r="B34" s="30" t="n">
         <v>2055</v>
       </c>
-      <c r="C34" s="27" t="n">
+      <c r="C34" s="30" t="n">
         <v>71</v>
       </c>
       <c r="D34" s="13" t="n">
@@ -4583,7 +4728,7 @@
       <c r="M34" s="13" t="n">
         <v>194066.93</v>
       </c>
-      <c r="N34" s="28" t="n">
+      <c r="N34" s="31" t="n">
         <v>0.2888</v>
       </c>
       <c r="O34" s="13" t="n">
@@ -4633,7 +4778,7 @@
       <c r="M35" s="6" t="n">
         <v>208648.51</v>
       </c>
-      <c r="N35" s="26" t="n">
+      <c r="N35" s="29" t="n">
         <v>0.2769</v>
       </c>
       <c r="O35" s="6" t="n">
@@ -4644,13 +4789,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="n">
+      <c r="A36" s="30" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="27" t="n">
+      <c r="B36" s="30" t="n">
         <v>2057</v>
       </c>
-      <c r="C36" s="27" t="n">
+      <c r="C36" s="30" t="n">
         <v>73</v>
       </c>
       <c r="D36" s="13" t="n">
@@ -4683,7 +4828,7 @@
       <c r="M36" s="13" t="n">
         <v>206972.27</v>
       </c>
-      <c r="N36" s="28" t="n">
+      <c r="N36" s="31" t="n">
         <v>0.2655</v>
       </c>
       <c r="O36" s="13" t="n">
@@ -4733,7 +4878,7 @@
       <c r="M37" s="6" t="n">
         <v>321904.01</v>
       </c>
-      <c r="N37" s="26" t="n">
+      <c r="N37" s="29" t="n">
         <v>0.2545</v>
       </c>
       <c r="O37" s="6" t="n">
@@ -4744,13 +4889,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="n">
+      <c r="A38" s="30" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="27" t="n">
+      <c r="B38" s="30" t="n">
         <v>2059</v>
       </c>
-      <c r="C38" s="27" t="n">
+      <c r="C38" s="30" t="n">
         <v>75</v>
       </c>
       <c r="D38" s="13" t="n">
@@ -4783,7 +4928,7 @@
       <c r="M38" s="13" t="n">
         <v>220737.25</v>
       </c>
-      <c r="N38" s="28" t="n">
+      <c r="N38" s="31" t="n">
         <v>0.244</v>
       </c>
       <c r="O38" s="13" t="n">
@@ -4833,7 +4978,7 @@
       <c r="M39" s="6" t="n">
         <v>232250.56</v>
       </c>
-      <c r="N39" s="26" t="n">
+      <c r="N39" s="29" t="n">
         <v>0.234</v>
       </c>
       <c r="O39" s="6" t="n">
@@ -4844,13 +4989,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="n">
+      <c r="A40" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="27" t="n">
+      <c r="B40" s="30" t="n">
         <v>2061</v>
       </c>
-      <c r="C40" s="27" t="n">
+      <c r="C40" s="30" t="n">
         <v>77</v>
       </c>
       <c r="D40" s="13" t="n">
@@ -4883,7 +5028,7 @@
       <c r="M40" s="13" t="n">
         <v>291487.14</v>
       </c>
-      <c r="N40" s="28" t="n">
+      <c r="N40" s="31" t="n">
         <v>0.2243</v>
       </c>
       <c r="O40" s="13" t="n">
@@ -4933,7 +5078,7 @@
       <c r="M41" s="6" t="n">
         <v>247745.96</v>
       </c>
-      <c r="N41" s="26" t="n">
+      <c r="N41" s="29" t="n">
         <v>0.2151</v>
       </c>
       <c r="O41" s="6" t="n">
@@ -4944,13 +5089,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="n">
+      <c r="A42" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="27" t="n">
+      <c r="B42" s="30" t="n">
         <v>2063</v>
       </c>
-      <c r="C42" s="27" t="n">
+      <c r="C42" s="30" t="n">
         <v>79</v>
       </c>
       <c r="D42" s="13" t="n">
@@ -4983,7 +5128,7 @@
       <c r="M42" s="13" t="n">
         <v>251079.26</v>
       </c>
-      <c r="N42" s="28" t="n">
+      <c r="N42" s="31" t="n">
         <v>0.2062</v>
       </c>
       <c r="O42" s="13" t="n">
@@ -4994,44 +5139,48 @@
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="22" t="inlineStr">
+      <c r="A43" s="22" t="n"/>
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D43" s="23" t="n">
+      <c r="D43" s="24" t="n">
         <v>104426.94</v>
       </c>
-      <c r="E43" s="23" t="n">
+      <c r="E43" s="24" t="n">
         <v>552099.14</v>
       </c>
-      <c r="F43" s="23" t="n">
+      <c r="F43" s="24" t="n">
         <v>48728.04</v>
       </c>
-      <c r="G43" s="23" t="n">
+      <c r="G43" s="24" t="n">
         <v>108360.58</v>
       </c>
-      <c r="H43" s="23" t="n">
+      <c r="H43" s="24" t="n">
         <v>49473.55</v>
       </c>
-      <c r="I43" s="23" t="n">
+      <c r="I43" s="24" t="n">
         <v>389740.26</v>
       </c>
-      <c r="J43" s="23" t="n">
+      <c r="J43" s="24" t="n">
         <v>4925371.48</v>
       </c>
-      <c r="K43" s="23" t="n">
+      <c r="K43" s="24" t="n">
         <v>28839.97</v>
       </c>
-      <c r="L43" s="23" t="n">
+      <c r="L43" s="24" t="n">
         <v>210514.92</v>
       </c>
-      <c r="M43" s="24" t="n">
+      <c r="M43" s="27" t="n">
         <v>6417554.89</v>
       </c>
-      <c r="O43" s="24" t="n">
+      <c r="N43" s="22" t="n"/>
+      <c r="O43" s="27" t="n">
         <v>2809609.01</v>
       </c>
+      <c r="P43" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5252,10 +5401,10 @@
           <t>medical_services — Medical Care Services</t>
         </is>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="28" t="n">
         <v>0.032</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="28" t="n">
         <v>0.01065891472868197</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -5275,10 +5424,10 @@
           <t>rx — Prescription Drugs</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="28" t="n">
         <v>0.025</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="28" t="n">
         <v>0.01756097560975611</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -5298,10 +5447,10 @@
           <t>dme — Durable Medical Equipment / Supplies</t>
         </is>
       </c>
-      <c r="B23" s="25" t="n">
+      <c r="B23" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="C23" s="25" t="n">
+      <c r="C23" s="28" t="n">
         <v>0.02254901960784306</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -5321,10 +5470,10 @@
           <t>facility — Hospital &amp; Facility Services</t>
         </is>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="28" t="n">
         <v>0.038</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="28" t="n">
         <v>0.00481695568400764</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -5344,10 +5493,10 @@
           <t>attendant_care_wage — Attendant / Home-Health Care (wage-based)</t>
         </is>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="28" t="n">
         <v>0.033</v>
       </c>
-      <c r="C25" s="25" t="n">
+      <c r="C25" s="28" t="n">
         <v>0.009680542110358292</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -5367,10 +5516,10 @@
           <t>general — General (CPI-U, all items)</t>
         </is>
       </c>
-      <c r="B26" s="25" t="n">
+      <c r="B26" s="28" t="n">
         <v>0.024</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="28" t="n">
         <v>0.0185546875</v>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -5391,42 +5540,42 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="16" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Cash-flow time from valuation for projection year y (0-based): m(y) = y + 0.5  [timing = mid_year].</t>
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="16" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Future (nominal) cost:  nominal_i(y) = current_i(y) × (1 + g_i)^m(y).</t>
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="16" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Present value:          pv_i(y) = nominal_i(y) / (1 + d)^m(y).</t>
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="16" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Equivalent net-discount form:  pv_i(y) = current_i(y) / (1 + r_i)^m(y),  r_i = (1+d)/(1+g_i) − 1.</t>
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="16" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Reasonable-value percentile policy: 80th percentile applied consistently across sources.</t>
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="16" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Final partial year of life expectancy is prorated by its fractional portion.</t>
@@ -5440,7 +5589,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="42" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
           <t>ILLUSTRATIVE: costs are stated at usual, customary, and reasonable value (billed-charge basis). Future insurance and Affordable Care Act coverage are treated as speculative and excluded, consistent with a robust collateral-source jurisdiction. Confirm the controlling rule for the actual venue.</t>
@@ -5539,22 +5688,26 @@
           <t>80</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>Allegheny County, PA (GAF)</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>Physiatry follow-up; Pain management visit; Physical therapy</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr"/>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>https://www.pmiconline.com/</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -5567,22 +5720,22 @@
           <t>80</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>National</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>Lumbar MRI; Spinal cord stimulator implant; SCS battery replacement</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>2026, 2026-05-01</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>https://www.va.gov/COMMUNITYCARE/revenue_ops/Reasonable_Charges.asp</t>
         </is>
@@ -5599,22 +5752,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>ZIP 152xx</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>Gabapentin; Baclofen</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>https://www.goodrx.com/</t>
         </is>
@@ -5631,22 +5784,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="32" t="inlineStr">
         <is>
           <t>Manual wheelchair</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>https://www.cms.gov/medicare/payment/fee-schedules/dmepos-fee-schedule</t>
         </is>
@@ -5663,22 +5816,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>TENS supplies</t>
         </is>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="F9" s="29" t="inlineStr"/>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>https://www.cms.gov/medicare/payment/fee-schedules/dmepos-fee-schedule</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -5691,22 +5848,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="32" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="32" t="inlineStr">
         <is>
           <t>Home health aide</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F10" s="29" t="inlineStr">
+      <c r="F10" s="32" t="inlineStr">
         <is>
           <t>https://www.genworth.com/aging-and-you/finances/cost-of-care.html</t>
         </is>
@@ -5723,22 +5880,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>Allegheny County, PA</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>Home accessibility modifications; Accessible vehicle modifications</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="F11" s="29" t="inlineStr"/>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -5748,7 +5909,7 @@
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>Medical Fees in the United States (Context4/PMIC)</t>
         </is>
@@ -5760,7 +5921,7 @@
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>Yale Wasserman</t>
         </is>
@@ -5772,7 +5933,7 @@
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>VA Reasonable Charges</t>
         </is>
@@ -5784,7 +5945,7 @@
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>CMS DMEPOS Fee Schedule</t>
         </is>
@@ -5796,7 +5957,7 @@
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t>Genworth Cost of Care Survey</t>
         </is>
@@ -5808,7 +5969,7 @@
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>American Hospital Directory (AHD)</t>
         </is>
@@ -5820,7 +5981,7 @@
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>GoodRx</t>
         </is>
@@ -5832,7 +5993,7 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>FAIR Health</t>
         </is>
@@ -5844,7 +6005,7 @@
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t>CDC/NCHS United States Life Tables</t>
         </is>
@@ -5856,7 +6017,7 @@
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>BLS CPI-U, Medical Care</t>
         </is>
@@ -5868,7 +6029,7 @@
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>U.S. Treasury Constant Maturity (H.15)</t>
         </is>
@@ -5937,7 +6098,7 @@
       </c>
     </row>
     <row r="5" ht="45" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -5949,7 +6110,7 @@
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -5969,7 +6130,7 @@
       </c>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -5981,7 +6142,7 @@
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -5993,7 +6154,7 @@
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6013,7 +6174,7 @@
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6025,7 +6186,7 @@
       </c>
     </row>
     <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6037,7 +6198,7 @@
       </c>
     </row>
     <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6057,26 +6218,26 @@
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Every recommended good or service is tied to a treating-provider recommendation or the medical record (Consensus Statement 64; IALCP Standard 3.3). A non-physician planner does not supply independent medical opinions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
+          <t>Every recommended good or service is tied to a treating-provider recommendation or the medical record (consistent with Consensus Statement 64 and the IALCP Standards of Practice, 4th ed.). A non-physician planner does not supply independent medical opinions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>This requirement reflects the controlling case law: plans built on templates or the planner's own unsupported beliefs have been excluded (Gunn v. Atchison), as has care not recommended by the treating providers (Anderson-Moody v. Wilson). The Medical Foundation tab documents the basis for each item and flags any gaps.</t>
+          <t>This reflects the consistent thrust of the case law: courts have excluded life care plans built on templates or the planner's own unsupported beliefs rather than the treating record, and have disallowed projected care that no treating physician or qualified medical expert recommended. The Medical Foundation tab documents the basis for each item and flags any gaps. Controlling authority varies by jurisdiction; counsel should cite the governing cases in the expert's report.</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6250,7 @@
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6101,7 +6262,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6121,7 +6282,7 @@
       </c>
     </row>
     <row r="27" ht="75" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6133,7 +6294,7 @@
       </c>
     </row>
     <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6153,7 +6314,7 @@
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6165,7 +6326,7 @@
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>•</t>
         </is>
@@ -6212,7 +6373,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each item's basis in a treating-provider recommendation or record (Gunn; Anderson-Moody)</t>
+          <t>Each item's basis in a treating-provider recommendation or the medical record</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6415,7 @@
           <t>Treating PM&amp;R physician, office note 2026-02-10, p.3</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6276,7 +6437,7 @@
           <t>Treating pain specialist, consult 2026-01-22</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6298,7 +6459,7 @@
           <t>Treating PM&amp;R physician, PT order 2026-02-10</t>
         </is>
       </c>
-      <c r="D7" s="32" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6320,7 +6481,7 @@
           <t>Treating psychiatrist, eval 2026-03-05</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6342,7 +6503,7 @@
           <t>Treating PM&amp;R physician, imaging plan 2026-02-10</t>
         </is>
       </c>
-      <c r="D9" s="32" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6364,7 +6525,7 @@
           <t>Treating pain specialist, med list 2026-01-22</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6386,7 +6547,7 @@
           <t>Treating PM&amp;R physician, med list 2026-02-10</t>
         </is>
       </c>
-      <c r="D11" s="32" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6408,7 +6569,7 @@
           <t>Treating PM&amp;R physician, DME order 2026-02-10</t>
         </is>
       </c>
-      <c r="D12" s="32" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6430,7 +6591,7 @@
           <t>Treating pain specialist, order 2026-01-22</t>
         </is>
       </c>
-      <c r="D13" s="32" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6452,7 +6613,7 @@
           <t>Treating pain specialist, surgical recommendation 2026-01-22</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6474,7 +6635,7 @@
           <t>Treating pain specialist, surgical recommendation 2026-01-22</t>
         </is>
       </c>
-      <c r="D15" s="32" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6496,7 +6657,7 @@
           <t>Treating PM&amp;R physician + functional assessment 2026-03-01</t>
         </is>
       </c>
-      <c r="D16" s="32" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6518,7 +6679,7 @@
           <t>OT home safety assessment 2026-03-12</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
@@ -6540,13 +6701,13 @@
           <t>OT mobility assessment 2026-03-12</t>
         </is>
       </c>
-      <c r="D18" s="32" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>documented</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="29" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>0 item(s) lack a documented medical foundation. A non-physician planner may not supply medical opinions; items without a treating-provider basis are vulnerable to exclusion.</t>
